--- a/010_ai_reviewer/レビュー観点抽出.xlsx
+++ b/010_ai_reviewer/レビュー観点抽出.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\azure_ai\education\010_ai_reviewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D597E28-CB6B-4A07-9CF5-1589194A30BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4099933-D5B5-4734-B4AA-E9CB9733C40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21060" windowHeight="15600" tabRatio="871" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="指摘一覧" sheetId="1" r:id="rId1"/>
     <sheet name="口癖" sheetId="2" r:id="rId2"/>
+    <sheet name="review_point" sheetId="3" r:id="rId3"/>
+    <sheet name="定数定義" sheetId="4" r:id="rId4"/>
+    <sheet name="具体例" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">review_point!$A$1:$C$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">具体例!$A$1:$C$61</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="196">
   <si>
     <t>年月日</t>
     <rPh sb="0" eb="3">
@@ -1161,6 +1168,1178 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>perspective_type</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>detail</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tabuchi</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>将来の予測・見込みを立てている場合、現時点での実績としてどうなっているかが表現されているか。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨソク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ミコ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>ゲンジテン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記載されている販売戦略について、営業部署と認識合わせおよび合意が出来ているか。</t>
+    <rPh sb="0" eb="2">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ハンバイセンリャク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>エイギョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ブショ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>ニンシキア</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ゴウイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>デキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品を使用する際の操作手順が、読み手に伝わるように記載されているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ソウサテジュン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツタ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品がどの業界・業種に対してニーズがあるのかが伝わるように記載されているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ギョウカイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ギョウシュ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ツタ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記載している費用で実現できるという理由が明確に説明されているか。</t>
+    <rPh sb="0" eb="2">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前回指摘した内容がある場合は、その指摘が反映されているか。</t>
+    <rPh sb="0" eb="4">
+      <t>ゼンカイシテキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他の既存の製品と比べて差別化が出来ているか。また、その差別化が妥当な内容であるか。</t>
+    <rPh sb="0" eb="1">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>クラ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>サベツカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>デキ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>サベツカ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ダトウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ製品でも顧客ごとに仕様を変える必要がある場合、その作業にかかるコストが考慮できているか。</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>コウリョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他の既存の製品との差別化について、その差別化に市場価値があるか。</t>
+    <rPh sb="0" eb="1">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>サベツカ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>サベツカ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>シジョウカチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自社の製品として売り出す場合、アピールポイントとなる部分が明確に記載されているか。</t>
+    <rPh sb="0" eb="2">
+      <t>ジシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品の売りとなる部分が明確になっているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品の売りとなる部分について、セールスポイントとなるキーワードが存在するか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品で実現したいサービス・機能の実現可能性について考慮されているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="18" eb="23">
+      <t>ジツゲンカノウセイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウリョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発する製品の試用方法について、どのような体験をユーザーに提供する想定か明記されているか。</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>シヨウホウホウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>タイケン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>テイキョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>メイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>将来の予測・見込みを立てている場合、その予測の数値が妥当であるかどうかの理由付けが明確にされているか。</t>
+    <rPh sb="0" eb="2">
+      <t>ショウライ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨソク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ミコ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヨソク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ダトウ</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>リユウヅ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品を売り出したいという意気込みが感じられるか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>イキゴ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記載されている販売戦略について、実現可能性が考慮できているか。</t>
+    <rPh sb="0" eb="2">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ハンバイセンリャク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>セイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コウリョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前回の指摘内容がどのように反映されているのかが明確になっているか。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンカイ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>シテキナイヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハンエイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ターゲット層を意識した開発・販売戦略になっているか。</t>
+    <rPh sb="5" eb="6">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イシキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="14" eb="18">
+      <t>ハンバイセンリャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>資料に記載されている内容が整理されているか。特に同じ欄に記載されている内容について、異なる観点の内容が含まれていないか。</t>
+    <rPh sb="0" eb="2">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>トク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>カンテン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>フク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品におけるAIの業務内容について明確になっているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ギョウムナイヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品にAIを使用することによる利点が明確になっているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>リテン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時系列順が存在する項目については、時系列順に並べることで読み手の負担を軽減できでいるか。</t>
+    <rPh sb="0" eb="4">
+      <t>ジケイレツジュン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソンザイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>ジケイレツジュン</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>テ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>フタン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ケイゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>資料全体から、開発する製品に対するイメージが掴めるような構成になっているか。</t>
+    <rPh sb="0" eb="4">
+      <t>シリョウゼンタイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品を導入したことによる顧客の業務への影響が考慮できているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ドウニュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>コキャク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コウリョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品を導入してもらうためにアピールできる対象が明確になっているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ドウニュウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>role</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>分類</t>
+  </si>
+  <si>
+    <t>確認観点</t>
+  </si>
+  <si>
+    <t>目的・意思決定</t>
+  </si>
+  <si>
+    <t>この資料で何を決めたいのか</t>
+  </si>
+  <si>
+    <t>課題定義・顧客価値</t>
+  </si>
+  <si>
+    <t>誰のどんな課題を解くのか</t>
+  </si>
+  <si>
+    <t>事業性・優先度</t>
+  </si>
+  <si>
+    <t>なぜ今やるべきか、効果は何か</t>
+  </si>
+  <si>
+    <t>AI適用妥当性・技術実現性</t>
+  </si>
+  <si>
+    <t>AIを使う必然性と実現可能性</t>
+  </si>
+  <si>
+    <t>データ・評価設計</t>
+  </si>
+  <si>
+    <t>必要データ、評価方法、成功条件は明確か</t>
+  </si>
+  <si>
+    <t>リスク・ガバナンス</t>
+  </si>
+  <si>
+    <t>安全性、法務、説明責任、運用統制に問題はないか</t>
+  </si>
+  <si>
+    <t>実行計画・体制</t>
+  </si>
+  <si>
+    <t>体制、予算、スケジュール、移行計画は妥当か</t>
+  </si>
+  <si>
+    <t>ストーリー・表現</t>
+  </si>
+  <si>
+    <t>論理の流れ、見やすさ、伝わりやすさ</t>
+  </si>
+  <si>
+    <t>主な確認観点</t>
+  </si>
+  <si>
+    <t>よくある指摘例</t>
+  </si>
+  <si>
+    <t>会議のゴール、意思決定者、承認範囲、依頼事項</t>
+  </si>
+  <si>
+    <t>この場で何を決めたいのか不明／PoC承認か本開発承認か曖昧</t>
+  </si>
+  <si>
+    <t>対象ユーザー、業務課題、困りごと、解決価値、現状の限界</t>
+  </si>
+  <si>
+    <t>AIを使いたいことが先行している／対象ユーザーが曖昧</t>
+  </si>
+  <si>
+    <t>売上、コスト削減、品質向上、競争優位、優先度</t>
+  </si>
+  <si>
+    <t>期待効果が定性的／なぜ今やるのか弱い</t>
+  </si>
+  <si>
+    <t>AI適用理由、方式選定、精度要件、性能要件、連携可能性</t>
+  </si>
+  <si>
+    <t>AIでなくルールベースでよいのでは／方式選定根拠が不足</t>
+  </si>
+  <si>
+    <t>データ所在、品質、量、教師データ、評価指標、成功条件</t>
+  </si>
+  <si>
+    <t>PoC成功条件がない／必要データの所在が不明</t>
+  </si>
+  <si>
+    <t>個人情報、機密情報、誤回答影響、バイアス、人手確認、責任分界</t>
+  </si>
+  <si>
+    <t>個人情報の扱い整理不足／誤回答時の影響評価がない</t>
+  </si>
+  <si>
+    <t>体制、予算、スケジュール、役割分担、PoC後の運用、移行条件</t>
+  </si>
+  <si>
+    <t>運用責任者が不明／スケジュールが楽観的</t>
+  </si>
+  <si>
+    <t>結論先行、1スライド1メッセージ、流れ、用語、見やすさ、図表</t>
+  </si>
+  <si>
+    <t>1枚に情報を詰め込みすぎ／専門用語が多い</t>
+  </si>
+  <si>
+    <t>common</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>code</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>purpose</t>
+  </si>
+  <si>
+    <t>purpose</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>assignment</t>
+  </si>
+  <si>
+    <t>assignment</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>priority</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>feasibility</t>
+  </si>
+  <si>
+    <t>feasibility</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>evaluation</t>
+  </si>
+  <si>
+    <t>evaluation</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>risk</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>plan</t>
+  </si>
+  <si>
+    <t>plan</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>story</t>
+  </si>
+  <si>
+    <t>story</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>具体的な指摘文面</t>
+  </si>
+  <si>
+    <t>この資料を通じて何を承認・判断してほしいのかが明確になっているか。</t>
+  </si>
+  <si>
+    <t>この資料を通じて何を承認・判断してほしいのかが明確になっているか。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>報告資料なのか提案資料なのかなど、資料の位置づけが明確になっているか。</t>
+    <rPh sb="25" eb="27">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>補足している内容と、資料の記載内容にズレがないかどうか。</t>
+    <rPh sb="0" eb="2">
+      <t>ホソク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>意思決定に必要な比較材料が整理されているか。</t>
+  </si>
+  <si>
+    <t>意思決定に必要な比較材料が整理されているか。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現行業務の流れや課題発生ポイントが明確になっているか。</t>
+    <rPh sb="17" eb="19">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者にとっての価値が明確になっているか。</t>
+    <rPh sb="11" eb="13">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課題起点ではなくAI活用ありきの製品になってしまってないか。</t>
+    <rPh sb="16" eb="18">
+      <t>セイヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期投資と継続コストに対して、どの程度で回収できるのかの見通しが明確になっているか。</t>
+    <rPh sb="28" eb="30">
+      <t>ミトオ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>短期効果と中長期の戦略価値が混在してしまっていないか。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザーが実際に使う前提が弱く、効果創出までの事業仮説が説得力のあるものになっているか。</t>
+    <rPh sb="28" eb="31">
+      <t>セットクリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この課題に対してAIを使う必然性が明確に説明されているか。</t>
+    <rPh sb="17" eb="19">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品導入に必要な精度水準が明確になっているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PoCが成功したと判断する条件が明確に定義されているか。</t>
+    <rPh sb="16" eb="18">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1スライドに複数の論点が入っており、主張がぼやけてしまっていないか。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報を詰め込みすぎてしまってないか。</t>
+  </si>
+  <si>
+    <t>情報を詰め込みすぎてしまってないか。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>用語や表記が資料全体で統一されているか。</t>
+    <rPh sb="6" eb="10">
+      <t>シリョウゼンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課題・解決策・効果の流れが伝わりやすい構成順になっているか。</t>
+    <rPh sb="13" eb="14">
+      <t>ツタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品を使用した際のユーザーに対する利益が、明確に記載されているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>リエキ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発プロセスとして記載しているスケジュールや作業工数の見積もりは現実的か。</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>サギョウコウスウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ミツ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ゲンジツテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自社の利益につながる形でアイディア化できているか。またそれが明確になっているか。</t>
+    <rPh sb="0" eb="2">
+      <t>ジシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リエキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>効果創出までの事業仮説が説得力のあるものになっているか。</t>
+    <rPh sb="12" eb="15">
+      <t>セットクリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品を使用するターゲット像が明確に定義されているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ゾウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>メイカク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ターゲット層はこの製品を導入する資産的余裕があるのかが考慮できているか。</t>
+    <rPh sb="5" eb="6">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ドウニュウ</t>
+    </rPh>
+    <rPh sb="16" eb="21">
+      <t>シサンテキヨユウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウリョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品がBtoBなのかBtoCなのかが明確になっているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品を使用するターゲット層に対して、この商品を導入したいかどうかの事前調査が出来ているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ドウニュウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>デキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検証に必要なデータを取得する方法が明確になっているか。</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>メイカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検証に必要なデータを取得する方法が実現可能性の観点から妥当であるか。</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="17" eb="22">
+      <t>ジツゲンカノウセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カンテン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ダトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品で実現したいサービス・機能を実現するための課題や懸念点について記載されているか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>この製品の品質として記載されている評価基準は妥当であるか。</t>
+    <rPh sb="2" eb="4">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>ヒョウカキジュン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ダトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発する製品に合わせた営業戦略が想定されているか。</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>エイギョウセンリャク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ソウテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1170,9 +2349,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1182,6 +2361,24 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1208,12 +2405,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1927,4 +3126,1326 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D1525E-7ADA-4E15-B2DE-DF569BAC4004}">
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="125.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C18" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" t="s">
+        <v>157</v>
+      </c>
+      <c r="C32" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" t="s">
+        <v>150</v>
+      </c>
+      <c r="C38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>144</v>
+      </c>
+      <c r="B41" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" t="s">
+        <v>159</v>
+      </c>
+      <c r="C43" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B47" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>144</v>
+      </c>
+      <c r="B50" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" t="s">
+        <v>159</v>
+      </c>
+      <c r="C51" t="s">
+        <v>181</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF316D46-F8F8-46D3-8754-1F113D8A006E}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD81983-1FD7-4B42-8B7E-20275EA6D48C}">
+  <sheetPr filterMode="1">
+    <tabColor theme="0" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:C61"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" hidden="1">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" hidden="1">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" hidden="1">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" hidden="1">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" hidden="1">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" hidden="1">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" hidden="1">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" hidden="1">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" hidden="1">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" hidden="1">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" hidden="1">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" hidden="1">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" hidden="1">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" hidden="1">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" hidden="1">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" hidden="1">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" hidden="1">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" hidden="1">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" hidden="1">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" hidden="1">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" hidden="1">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" hidden="1">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" hidden="1">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" hidden="1">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" hidden="1">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" hidden="1">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" hidden="1">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" hidden="1">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" hidden="1">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" hidden="1">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" hidden="1">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" hidden="1">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>159</v>
+      </c>
+      <c r="C61" t="s">
+        <v>181</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C61" xr:uid="{BBD81983-1FD7-4B42-8B7E-20275EA6D48C}">
+    <filterColumn colId="2">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/010_ai_reviewer/レビュー観点抽出.xlsx
+++ b/010_ai_reviewer/レビュー観点抽出.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\azure_ai\education\010_ai_reviewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4099933-D5B5-4734-B4AA-E9CB9733C40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEA098C-07FD-48DA-80FC-9FB07AD118FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21060" windowHeight="15600" tabRatio="871" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="871" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="指摘一覧" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="198">
   <si>
     <t>年月日</t>
     <rPh sb="0" eb="3">
@@ -2340,6 +2340,50 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>ソウテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他社製品と比べて差別化できている点が伝わるような構成になっているか</t>
+    <rPh sb="0" eb="4">
+      <t>タシャセイヒン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>クラ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>サベツカ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツタ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>導入検討者に対して、こちらが課題として掲げている項目が刺さっているか</t>
+    <rPh sb="0" eb="5">
+      <t>ドウニュウケントウシャ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>サ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2693,7 +2737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E59"/>
+  <dimension ref="B2:E62"/>
   <sheetFormatPr defaultColWidth="3.5" defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="3" width="13.5" style="1" customWidth="1"/>
@@ -3040,6 +3084,30 @@
     <row r="59" spans="2:4">
       <c r="D59" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="1">
+        <v>46178</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D60" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="D61" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" s="1">
+        <v>46188</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
